--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/ARIZONA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/ARIZONA_2016.xlsx
@@ -2389,7 +2389,7 @@
         <v>106</v>
       </c>
       <c r="D113">
-        <v>0.009133206961916249</v>
+        <v>0.009133206961916248</v>
       </c>
     </row>
     <row r="114">
@@ -3721,7 +3721,7 @@
         <v>11</v>
       </c>
       <c r="D187">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="188">
@@ -5395,7 +5395,7 @@
         <v>11</v>
       </c>
       <c r="D280">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="281">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C286">
@@ -6151,7 +6151,7 @@
         <v>11</v>
       </c>
       <c r="D322">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="323">
@@ -6583,7 +6583,7 @@
         <v>11</v>
       </c>
       <c r="D346">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="347">
@@ -6637,7 +6637,7 @@
         <v>11</v>
       </c>
       <c r="D349">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="350">
@@ -7375,7 +7375,7 @@
         <v>11</v>
       </c>
       <c r="D390">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="391">
@@ -9175,7 +9175,7 @@
         <v>11</v>
       </c>
       <c r="D490">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="491">
@@ -9931,7 +9931,7 @@
         <v>11</v>
       </c>
       <c r="D532">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="533">
@@ -10561,7 +10561,7 @@
         <v>11</v>
       </c>
       <c r="D567">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="568">
@@ -10687,7 +10687,7 @@
         <v>11</v>
       </c>
       <c r="D574">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="575">
@@ -11695,7 +11695,7 @@
         <v>11</v>
       </c>
       <c r="D630">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="631">
@@ -12271,7 +12271,7 @@
         <v>11</v>
       </c>
       <c r="D662">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="663">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C728">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 26-</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C729">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C748">
@@ -16555,7 +16555,7 @@
         <v>11</v>
       </c>
       <c r="D900">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="901">
@@ -19705,7 +19705,7 @@
         <v>11</v>
       </c>
       <c r="D1075">
-        <v>0.0009477856281233845</v>
+        <v>0.0009477856281233844</v>
       </c>
     </row>
     <row r="1076">
